--- a/modeleLogiqueCorps/ig/StructureDefinition-fr-cda-prescription-dispositifs-medicaux.xlsx
+++ b/modeleLogiqueCorps/ig/StructureDefinition-fr-cda-prescription-dispositifs-medicaux.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2343" uniqueCount="280">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2357" uniqueCount="294">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-15T12:22:25+00:00</t>
+    <t>2026-06-30T08:22:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -454,6 +454,9 @@
 </t>
   </si>
   <si>
+    <t>Can serve as a target of a linkHtml reference</t>
+  </si>
+  <si>
     <t>Section.classCode</t>
   </si>
   <si>
@@ -643,6 +646,9 @@
     <t>Titre de la section</t>
   </si>
   <si>
+    <t>If valued, it is to be rendered as part of the narrative content of the clinical document body.</t>
+  </si>
+  <si>
     <t>Section.text</t>
   </si>
   <si>
@@ -656,10 +662,25 @@
     <t>Bloc narratif de la section</t>
   </si>
   <si>
+    <t>Also referred to as the CDA Narrative Block</t>
+  </si>
+  <si>
     <t>Section.confidentialityCode</t>
   </si>
   <si>
+    <t>Controls the disclosure of information in this section</t>
+  </si>
+  <si>
+    <t>A value for Section.confidentialityCode overrides the value propagated from StructuredBody.</t>
+  </si>
+  <si>
     <t>Section.languageCode</t>
+  </si>
+  <si>
+    <t>Human language of character data</t>
+  </si>
+  <si>
+    <t>A value for Section.languageCode overrides the value propagated from StructuredBody.</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/all-languages</t>
@@ -672,6 +693,15 @@
 </t>
   </si>
   <si>
+    <t>Primary target of the entries recorded in a section</t>
+  </si>
+  <si>
+    <t>Most of the time the subject is the same as the recordTarget, but need not be, for instance when the subject is a fetus observed in an obstetrical ultrasound.</t>
+  </si>
+  <si>
+    <t>The subject participant can be ascribed to a CDA section or a CDA entry. It propagates to nested components, unless overridden. The subject of a document is presumed to be the patient.</t>
+  </si>
+  <si>
     <t>Section.author</t>
   </si>
   <si>
@@ -686,6 +716,9 @@
     <t>Auteur de la prescription</t>
   </si>
   <si>
+    <t>The author participant can be ascribed to a CDA section, where it overrides the value(s) propagated from the CDA header.</t>
+  </si>
+  <si>
     <t>Section.informant</t>
   </si>
   <si>
@@ -693,6 +726,9 @@
 </t>
   </si>
   <si>
+    <t>The informant participant can be ascribed to a CDA section where it overrides the value(s) propagated from the CDA header.</t>
+  </si>
+  <si>
     <t>Section.entry</t>
   </si>
   <si>
@@ -846,6 +882,12 @@
   <si>
     <t xml:space="preserve">http://hl7.org/cda/stds/core/StructureDefinition/InfrastructureRoot
 </t>
+  </si>
+  <si>
+    <t>Used to nest a Section within a Section</t>
+  </si>
+  <si>
+    <t>Context propagates to nested sections</t>
   </si>
   <si>
     <t>Section.component.nullFlavor</t>
@@ -1222,7 +1264,7 @@
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
-    <col min="15" max="15" width="13.4296875" customWidth="true" bestFit="true"/>
+    <col min="15" max="15" width="148.87109375" customWidth="true" bestFit="true"/>
     <col min="16" max="16" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
@@ -3025,7 +3067,9 @@
       <c r="K18" t="s" s="2">
         <v>141</v>
       </c>
-      <c r="L18" s="2"/>
+      <c r="L18" t="s" s="2">
+        <v>142</v>
+      </c>
       <c r="M18" s="2"/>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -3096,10 +3140,10 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -3133,7 +3177,7 @@
       </c>
       <c r="Q19" s="2"/>
       <c r="R19" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="S19" t="s" s="2">
         <v>74</v>
@@ -3155,7 +3199,7 @@
       </c>
       <c r="Y19" s="2"/>
       <c r="Z19" t="s" s="2">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="AA19" t="s" s="2">
         <v>74</v>
@@ -3173,7 +3217,7 @@
         <v>74</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>80</v>
@@ -3193,10 +3237,10 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -3230,7 +3274,7 @@
       </c>
       <c r="Q20" s="2"/>
       <c r="R20" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="S20" t="s" s="2">
         <v>74</v>
@@ -3252,7 +3296,7 @@
       </c>
       <c r="Y20" s="2"/>
       <c r="Z20" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="AA20" t="s" s="2">
         <v>74</v>
@@ -3270,7 +3314,7 @@
         <v>74</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>80</v>
@@ -3290,10 +3334,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -3307,7 +3351,7 @@
         <v>75</v>
       </c>
       <c r="H21" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="I21" t="s" s="2">
         <v>74</v>
@@ -3319,10 +3363,10 @@
         <v>95</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -3373,7 +3417,7 @@
         <v>74</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>80</v>
@@ -3393,10 +3437,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -3410,7 +3454,7 @@
         <v>75</v>
       </c>
       <c r="H22" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="I22" t="s" s="2">
         <v>74</v>
@@ -3419,13 +3463,13 @@
         <v>74</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
@@ -3476,7 +3520,7 @@
         <v>74</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>80</v>
@@ -3496,10 +3540,10 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -3597,10 +3641,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -3616,7 +3660,7 @@
         <v>75</v>
       </c>
       <c r="H24" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="I24" t="s" s="2">
         <v>74</v>
@@ -3629,7 +3673,7 @@
       </c>
       <c r="L24" s="2"/>
       <c r="M24" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -3641,7 +3685,7 @@
         <v>74</v>
       </c>
       <c r="S24" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="T24" t="s" s="2">
         <v>74</v>
@@ -3680,7 +3724,7 @@
         <v>74</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>80</v>
@@ -3700,17 +3744,17 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E25" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="F25" t="s" s="2">
         <v>75</v>
@@ -3719,7 +3763,7 @@
         <v>75</v>
       </c>
       <c r="H25" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="I25" t="s" s="2">
         <v>74</v>
@@ -3732,7 +3776,7 @@
       </c>
       <c r="L25" s="2"/>
       <c r="M25" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
@@ -3744,7 +3788,7 @@
         <v>74</v>
       </c>
       <c r="S25" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="T25" t="s" s="2">
         <v>74</v>
@@ -3783,7 +3827,7 @@
         <v>74</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>80</v>
@@ -3803,17 +3847,17 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E26" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="F26" t="s" s="2">
         <v>80</v>
@@ -3835,7 +3879,7 @@
       </c>
       <c r="L26" s="2"/>
       <c r="M26" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
@@ -3847,7 +3891,7 @@
         <v>74</v>
       </c>
       <c r="S26" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="T26" t="s" s="2">
         <v>74</v>
@@ -3886,7 +3930,7 @@
         <v>74</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>80</v>
@@ -3906,17 +3950,17 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E27" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F27" t="s" s="2">
         <v>80</v>
@@ -3938,7 +3982,7 @@
       </c>
       <c r="L27" s="2"/>
       <c r="M27" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
@@ -3989,7 +4033,7 @@
         <v>74</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>80</v>
@@ -4009,17 +4053,17 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E28" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F28" t="s" s="2">
         <v>75</v>
@@ -4028,7 +4072,7 @@
         <v>75</v>
       </c>
       <c r="H28" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="I28" t="s" s="2">
         <v>74</v>
@@ -4041,7 +4085,7 @@
       </c>
       <c r="L28" s="2"/>
       <c r="M28" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -4053,7 +4097,7 @@
         <v>74</v>
       </c>
       <c r="S28" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="T28" t="s" s="2">
         <v>74</v>
@@ -4092,7 +4136,7 @@
         <v>74</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>80</v>
@@ -4112,10 +4156,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4138,11 +4182,11 @@
         <v>74</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="L29" s="2"/>
       <c r="M29" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
@@ -4193,7 +4237,7 @@
         <v>74</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>80</v>
@@ -4213,10 +4257,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -4243,7 +4287,7 @@
       </c>
       <c r="L30" s="2"/>
       <c r="M30" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -4294,7 +4338,7 @@
         <v>74</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>80</v>
@@ -4314,17 +4358,17 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E31" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="F31" t="s" s="2">
         <v>80</v>
@@ -4342,11 +4386,11 @@
         <v>74</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="L31" s="2"/>
       <c r="M31" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -4397,7 +4441,7 @@
         <v>74</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>80</v>
@@ -4417,17 +4461,17 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E32" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F32" t="s" s="2">
         <v>80</v>
@@ -4445,11 +4489,11 @@
         <v>74</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="L32" s="2"/>
       <c r="M32" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -4500,7 +4544,7 @@
         <v>74</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>80</v>
@@ -4520,17 +4564,17 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E33" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="F33" t="s" s="2">
         <v>80</v>
@@ -4548,11 +4592,11 @@
         <v>74</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="L33" s="2"/>
       <c r="M33" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -4603,7 +4647,7 @@
         <v>74</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>80</v>
@@ -4623,10 +4667,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -4640,7 +4684,7 @@
         <v>75</v>
       </c>
       <c r="H34" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="I34" t="s" s="2">
         <v>74</v>
@@ -4649,16 +4693,18 @@
         <v>74</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="N34" s="2"/>
-      <c r="O34" s="2"/>
+      <c r="O34" t="s" s="2">
+        <v>204</v>
+      </c>
       <c r="P34" t="s" s="2">
         <v>74</v>
       </c>
@@ -4706,7 +4752,7 @@
         <v>74</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>80</v>
@@ -4726,10 +4772,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -4743,7 +4789,7 @@
         <v>75</v>
       </c>
       <c r="H35" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="I35" t="s" s="2">
         <v>74</v>
@@ -4752,15 +4798,17 @@
         <v>74</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>206</v>
-      </c>
-      <c r="N35" s="2"/>
+        <v>208</v>
+      </c>
+      <c r="N35" t="s" s="2">
+        <v>209</v>
+      </c>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
         <v>74</v>
@@ -4809,7 +4857,7 @@
         <v>74</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>80</v>
@@ -4829,10 +4877,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -4855,12 +4903,16 @@
         <v>74</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>152</v>
-      </c>
-      <c r="L36" s="2"/>
+        <v>153</v>
+      </c>
+      <c r="L36" t="s" s="2">
+        <v>211</v>
+      </c>
       <c r="M36" s="2"/>
       <c r="N36" s="2"/>
-      <c r="O36" s="2"/>
+      <c r="O36" t="s" s="2">
+        <v>212</v>
+      </c>
       <c r="P36" t="s" s="2">
         <v>74</v>
       </c>
@@ -4908,7 +4960,7 @@
         <v>74</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>80</v>
@@ -4928,10 +4980,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -4956,10 +5008,14 @@
       <c r="K37" t="s" s="2">
         <v>91</v>
       </c>
-      <c r="L37" s="2"/>
+      <c r="L37" t="s" s="2">
+        <v>214</v>
+      </c>
       <c r="M37" s="2"/>
       <c r="N37" s="2"/>
-      <c r="O37" s="2"/>
+      <c r="O37" t="s" s="2">
+        <v>215</v>
+      </c>
       <c r="P37" t="s" s="2">
         <v>74</v>
       </c>
@@ -4987,7 +5043,7 @@
       </c>
       <c r="Y37" s="2"/>
       <c r="Z37" t="s" s="2">
-        <v>209</v>
+        <v>216</v>
       </c>
       <c r="AA37" t="s" s="2">
         <v>74</v>
@@ -5005,7 +5061,7 @@
         <v>74</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>80</v>
@@ -5025,10 +5081,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -5051,12 +5107,18 @@
         <v>74</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>211</v>
-      </c>
-      <c r="L38" s="2"/>
+        <v>218</v>
+      </c>
+      <c r="L38" t="s" s="2">
+        <v>219</v>
+      </c>
       <c r="M38" s="2"/>
-      <c r="N38" s="2"/>
-      <c r="O38" s="2"/>
+      <c r="N38" t="s" s="2">
+        <v>220</v>
+      </c>
+      <c r="O38" t="s" s="2">
+        <v>221</v>
+      </c>
       <c r="P38" t="s" s="2">
         <v>74</v>
       </c>
@@ -5104,7 +5166,7 @@
         <v>74</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>80</v>
@@ -5124,10 +5186,10 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>212</v>
+        <v>222</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>212</v>
+        <v>222</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -5141,7 +5203,7 @@
         <v>75</v>
       </c>
       <c r="H39" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="I39" t="s" s="2">
         <v>74</v>
@@ -5150,16 +5212,18 @@
         <v>74</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>213</v>
+        <v>223</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>214</v>
+        <v>224</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>215</v>
+        <v>225</v>
       </c>
       <c r="N39" s="2"/>
-      <c r="O39" s="2"/>
+      <c r="O39" t="s" s="2">
+        <v>226</v>
+      </c>
       <c r="P39" t="s" s="2">
         <v>74</v>
       </c>
@@ -5207,7 +5271,7 @@
         <v>74</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>212</v>
+        <v>222</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>80</v>
@@ -5227,10 +5291,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>216</v>
+        <v>227</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>216</v>
+        <v>227</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -5253,12 +5317,14 @@
         <v>74</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>217</v>
+        <v>228</v>
       </c>
       <c r="L40" s="2"/>
       <c r="M40" s="2"/>
       <c r="N40" s="2"/>
-      <c r="O40" s="2"/>
+      <c r="O40" t="s" s="2">
+        <v>229</v>
+      </c>
       <c r="P40" t="s" s="2">
         <v>74</v>
       </c>
@@ -5306,7 +5372,7 @@
         <v>74</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>216</v>
+        <v>227</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>80</v>
@@ -5326,10 +5392,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>218</v>
+        <v>230</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>218</v>
+        <v>230</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -5343,7 +5409,7 @@
         <v>81</v>
       </c>
       <c r="H41" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="I41" t="s" s="2">
         <v>74</v>
@@ -5352,10 +5418,10 @@
         <v>74</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>219</v>
+        <v>231</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>220</v>
+        <v>232</v>
       </c>
       <c r="M41" s="2"/>
       <c r="N41" s="2"/>
@@ -5407,7 +5473,7 @@
         <v>74</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>218</v>
+        <v>230</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>80</v>
@@ -5427,10 +5493,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>221</v>
+        <v>233</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>221</v>
+        <v>233</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -5528,10 +5594,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>222</v>
+        <v>234</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>222</v>
+        <v>234</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -5629,10 +5695,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>223</v>
+        <v>235</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>223</v>
+        <v>235</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -5730,10 +5796,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>224</v>
+        <v>236</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>224</v>
+        <v>236</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -5831,10 +5897,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>225</v>
+        <v>237</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>225</v>
+        <v>237</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -5934,10 +6000,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>226</v>
+        <v>238</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>226</v>
+        <v>238</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -6037,10 +6103,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>227</v>
+        <v>239</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>227</v>
+        <v>239</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -6140,10 +6206,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>228</v>
+        <v>240</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>228</v>
+        <v>240</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -6243,10 +6309,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>229</v>
+        <v>241</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>229</v>
+        <v>241</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -6344,10 +6410,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>230</v>
+        <v>242</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>230</v>
+        <v>242</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -6377,7 +6443,7 @@
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
-        <v>231</v>
+        <v>243</v>
       </c>
       <c r="Q51" s="2"/>
       <c r="R51" t="s" s="2">
@@ -6403,7 +6469,7 @@
       </c>
       <c r="Y51" s="2"/>
       <c r="Z51" t="s" s="2">
-        <v>232</v>
+        <v>244</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>74</v>
@@ -6421,7 +6487,7 @@
         <v>74</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>233</v>
+        <v>245</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
@@ -6441,10 +6507,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>234</v>
+        <v>246</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>234</v>
+        <v>246</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -6478,7 +6544,7 @@
       </c>
       <c r="Q52" s="2"/>
       <c r="R52" t="s" s="2">
-        <v>235</v>
+        <v>247</v>
       </c>
       <c r="S52" t="s" s="2">
         <v>74</v>
@@ -6520,7 +6586,7 @@
         <v>74</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>236</v>
+        <v>248</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
@@ -6540,10 +6606,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>237</v>
+        <v>249</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>237</v>
+        <v>249</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -6566,7 +6632,7 @@
         <v>74</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>238</v>
+        <v>250</v>
       </c>
       <c r="L53" s="2"/>
       <c r="M53" s="2"/>
@@ -6619,7 +6685,7 @@
         <v>74</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>239</v>
+        <v>251</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
@@ -6639,10 +6705,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>240</v>
+        <v>252</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>240</v>
+        <v>252</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -6665,7 +6731,7 @@
         <v>74</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>241</v>
+        <v>253</v>
       </c>
       <c r="L54" s="2"/>
       <c r="M54" s="2"/>
@@ -6718,7 +6784,7 @@
         <v>74</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>242</v>
+        <v>254</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>80</v>
@@ -6738,10 +6804,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>243</v>
+        <v>255</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>243</v>
+        <v>255</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -6764,7 +6830,7 @@
         <v>74</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>244</v>
+        <v>256</v>
       </c>
       <c r="L55" s="2"/>
       <c r="M55" s="2"/>
@@ -6817,7 +6883,7 @@
         <v>74</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>245</v>
+        <v>257</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>80</v>
@@ -6837,10 +6903,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>246</v>
+        <v>258</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>246</v>
+        <v>258</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -6863,7 +6929,7 @@
         <v>74</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>247</v>
+        <v>259</v>
       </c>
       <c r="L56" s="2"/>
       <c r="M56" s="2"/>
@@ -6916,7 +6982,7 @@
         <v>74</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>248</v>
+        <v>260</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>80</v>
@@ -6936,10 +7002,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>249</v>
+        <v>261</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>249</v>
+        <v>261</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -6962,7 +7028,7 @@
         <v>74</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>250</v>
+        <v>262</v>
       </c>
       <c r="L57" s="2"/>
       <c r="M57" s="2"/>
@@ -7015,7 +7081,7 @@
         <v>74</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>251</v>
+        <v>263</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>80</v>
@@ -7035,10 +7101,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>252</v>
+        <v>264</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>252</v>
+        <v>264</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -7061,7 +7127,7 @@
         <v>74</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>253</v>
+        <v>265</v>
       </c>
       <c r="L58" s="2"/>
       <c r="M58" s="2"/>
@@ -7114,7 +7180,7 @@
         <v>74</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>254</v>
+        <v>266</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>80</v>
@@ -7134,10 +7200,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>255</v>
+        <v>267</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>255</v>
+        <v>267</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -7160,7 +7226,7 @@
         <v>74</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>256</v>
+        <v>268</v>
       </c>
       <c r="L59" s="2"/>
       <c r="M59" s="2"/>
@@ -7213,7 +7279,7 @@
         <v>74</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>257</v>
+        <v>269</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>80</v>
@@ -7233,10 +7299,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>258</v>
+        <v>270</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>258</v>
+        <v>270</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -7259,7 +7325,7 @@
         <v>74</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>259</v>
+        <v>271</v>
       </c>
       <c r="L60" s="2"/>
       <c r="M60" s="2"/>
@@ -7312,7 +7378,7 @@
         <v>74</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>260</v>
+        <v>272</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>80</v>
@@ -7332,10 +7398,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>261</v>
+        <v>273</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>261</v>
+        <v>273</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -7358,7 +7424,7 @@
         <v>74</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>262</v>
+        <v>274</v>
       </c>
       <c r="L61" s="2"/>
       <c r="M61" s="2"/>
@@ -7411,7 +7477,7 @@
         <v>74</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>263</v>
+        <v>275</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>80</v>
@@ -7431,10 +7497,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>264</v>
+        <v>276</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>264</v>
+        <v>276</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -7457,12 +7523,16 @@
         <v>74</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>265</v>
-      </c>
-      <c r="L62" s="2"/>
+        <v>277</v>
+      </c>
+      <c r="L62" t="s" s="2">
+        <v>278</v>
+      </c>
       <c r="M62" s="2"/>
       <c r="N62" s="2"/>
-      <c r="O62" s="2"/>
+      <c r="O62" t="s" s="2">
+        <v>279</v>
+      </c>
       <c r="P62" t="s" s="2">
         <v>74</v>
       </c>
@@ -7510,7 +7580,7 @@
         <v>74</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>264</v>
+        <v>276</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>80</v>
@@ -7530,10 +7600,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>266</v>
+        <v>280</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>266</v>
+        <v>280</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -7631,10 +7701,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>267</v>
+        <v>281</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>267</v>
+        <v>281</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -7732,10 +7802,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>268</v>
+        <v>282</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>268</v>
+        <v>282</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -7833,10 +7903,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>269</v>
+        <v>283</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>269</v>
+        <v>283</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -7934,10 +8004,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>270</v>
+        <v>284</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>270</v>
+        <v>284</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -8037,10 +8107,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>271</v>
+        <v>285</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>271</v>
+        <v>285</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -8140,10 +8210,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>272</v>
+        <v>286</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>272</v>
+        <v>286</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -8243,10 +8313,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>273</v>
+        <v>287</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>273</v>
+        <v>287</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -8346,10 +8416,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>274</v>
+        <v>288</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>274</v>
+        <v>288</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -8447,10 +8517,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>275</v>
+        <v>289</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>275</v>
+        <v>289</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -8477,7 +8547,7 @@
       </c>
       <c r="L72" s="2"/>
       <c r="M72" t="s" s="2">
-        <v>276</v>
+        <v>290</v>
       </c>
       <c r="N72" s="2"/>
       <c r="O72" s="2"/>
@@ -8486,7 +8556,7 @@
       </c>
       <c r="Q72" s="2"/>
       <c r="R72" t="s" s="2">
-        <v>231</v>
+        <v>243</v>
       </c>
       <c r="S72" t="s" s="2">
         <v>74</v>
@@ -8528,7 +8598,7 @@
         <v>74</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>275</v>
+        <v>289</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>80</v>
@@ -8548,10 +8618,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>277</v>
+        <v>291</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>277</v>
+        <v>291</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -8585,7 +8655,7 @@
       </c>
       <c r="Q73" s="2"/>
       <c r="R73" t="s" s="2">
-        <v>235</v>
+        <v>247</v>
       </c>
       <c r="S73" t="s" s="2">
         <v>74</v>
@@ -8627,7 +8697,7 @@
         <v>74</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>277</v>
+        <v>291</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>80</v>
@@ -8647,10 +8717,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>278</v>
+        <v>292</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>278</v>
+        <v>292</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -8673,7 +8743,7 @@
         <v>74</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>279</v>
+        <v>293</v>
       </c>
       <c r="L74" s="2"/>
       <c r="M74" s="2"/>
@@ -8726,7 +8796,7 @@
         <v>74</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>278</v>
+        <v>292</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>75</v>
